--- a/quantexa_mock_data/adult_social_care_mosaic_extract.xlsx
+++ b/quantexa_mock_data/adult_social_care_mosaic_extract.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="READ_ME_EXTRACT" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ASC_Export'!$A$3:$W$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ASC_Export'!$A$3:$W$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,12 +50,8 @@
       <name val="Arial"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +71,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,19 +110,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,31 +489,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
     <col width="36" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
     <col width="70" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
@@ -517,14 +526,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Job: ASC_NIGHTLY_COHORT  Run: 2026-09-09 19:03  Operator: SVC-MOSAIC-ETL  Rowcount: 4  Filter: open OR closed_last_24m AND postcode in (M4,M15,M18,M22)</t>
+          <t>Job: ASC_NIGHTLY_COHORT  Run: 2026-09-09 19:03  Operator: SVC-MOSAIC-ETL  Rowcount: 6  Filter: open OR closed_last_24m AND postcode in (M4,M15,M18,M22)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1">
+    <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>ExportRun</t>
@@ -751,338 +760,564 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>2026-09-09 19:03</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Mosaic v21.8</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Manchester City Council</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>ASC/25/07712</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>PR-190221</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Smith John</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>73y male</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>03/11/1952</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Hulme Manchester, 9 Bonsall Court</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>M15 6EF</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>10093088055</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>2025-11-02</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>Reablement follow-up</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>Reablement</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>North Reablement</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>Davies P</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr">
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>WD-4412</t>
         </is>
       </c>
-      <c r="S5" s="4" t="inlineStr">
+      <c r="S5" s="5" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
       </c>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="inlineStr">
+      <c r="T5" s="5" t="inlineStr"/>
+      <c r="U5" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="V5" s="4" t="inlineStr">
+      <c r="V5" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="W5" s="4" t="inlineStr">
+      <c r="W5" s="5" t="inlineStr">
         <is>
           <t>Closed March 2026.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>2026-09-09 19:03</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Mosaic v21.8</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Manchester City Council</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>ASC/24/33081</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>PR-410002</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Okonkwo Mr P</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>57y male</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>1968-09-30</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>16 Bengal Street Ancoats Manchester</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>M4 6LN</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>10093022190</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>2024-02-11</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>Carer enquiry (not the carer)</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>Information only</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>Duty</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr">
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr">
+      <c r="S6" s="5" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr">
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="V6" s="4" t="inlineStr">
+      <c r="V6" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="W6" s="4" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>2026-09-09 19:03</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Mosaic v21.8</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Manchester City Council</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>ASC/26/08801</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>PR-552991</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Price Susan</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>70y female</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>19 Dec 1955</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Flat 3 Salisbury House, Wythenshawe</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>M22 5RF</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>10092881002</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Falls / OT</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>OT community</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>South OT</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>Khan A</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>WD-2281</t>
         </is>
       </c>
-      <c r="S7" s="4" t="inlineStr">
+      <c r="S7" s="5" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="T7" s="5" t="inlineStr">
         <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr">
+      <c r="U7" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="V7" s="4" t="inlineStr">
+      <c r="V7" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="W7" s="4" t="inlineStr"/>
+      <c r="W7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-09 19:03</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Mosaic v21.8</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Manchester City Council</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>ASC/26/14102</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>PR-901220</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Brennan / male</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>29y male</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Aug 1997</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Ancoats, 11 Poland St, Manchester</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>M4 6BN</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>10093300118</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>Homelessness prevention / rent arrears (housing referral)</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>Housing-related support</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>Open - low level</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>Unallocated Duty</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr"/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="T8" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="U8" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V8" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W8" s="6" t="inlineStr">
+        <is>
+          <t>No allocated worker. Housing NOSP on file. Duty contact only. Not Care Act.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09 19:03</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Mosaic v21.8</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Manchester City Council</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ASC/26/12880</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>PR-330140</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Nwosu / female</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>81y female</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Jan 1945</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Flat 7 Redhill Street, Ancoats Manchester</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>M4 5AE</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>10093411209</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>Neighbour concern - not seen / isolation</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>Community / early help</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>Open - low level</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>Unallocated Duty</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>No allocated worker. Concern from neighbour via housing officer. Lives alone. No Care Act assessment.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:W7"/>
+  <autoFilter ref="A3:W9"/>
   <mergeCells count="2">
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="A2:U2"/>
@@ -1104,7 +1339,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>This is a system extract. Do not edit. PersonRef is Mosaic internal and is not an NHS number.</t>
         </is>
